--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_395_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_395_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>19</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41:33</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>47:55</t>
+          <t>27:56</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,22 +1843,22 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>5</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>61:23</t>
+          <t>31:24</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>40:28</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40:40</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>52:17</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>58:35</t>
+          <t>28:35</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>24:31</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>100</v>
       </c>
       <c r="T30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4292,16 +4292,16 @@
         <v>16</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>4</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>48:40</t>
+          <t>28:40</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>30:29</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,22 +4604,22 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
           <t>14.8%</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>40:00</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>32:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
     </row>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>32:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,17 +5388,17 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>21.0%</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
           <t>8.2%</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>25:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,22 +5584,22 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -5664,16 +5664,16 @@
         <v>23</v>
       </c>
       <c r="T42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>6</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>71:22</t>
+          <t>31:24</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -6056,16 +6056,16 @@
         <v>11</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>3</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>36:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>41:35</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>120</v>
       </c>
       <c r="T48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>23</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_395_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_395_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>19</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>5</v>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2511,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>100</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4292,16 +4292,16 @@
         <v>16</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>4</v>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5664,16 +5664,16 @@
         <v>23</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>6</v>
@@ -6056,16 +6056,16 @@
         <v>11</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>3</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>120</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X48" t="n">
         <v>23</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_395_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_395_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>9</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>79.31</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -2178,11 +2178,11 @@
         <v>2</v>
       </c>
       <c r="AK21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>10</v>
       </c>
       <c r="X48" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
